--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2923,6 +2923,1382 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120476080</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>515086</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7128233</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120474982</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>515116</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7128353</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120475900</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>353</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515034</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7128245</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120475510</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515134</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7128286</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120474789</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>515098</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7128433</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120475672</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>515151</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7128276</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120474748</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>515115</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7128454</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120474995</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>515125</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7128350</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120474577</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>515097</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7128458</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120474889</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>515128</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7128396</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120475071</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91146</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>760</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>515108</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7128363</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120474395</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>515054</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7128523</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120475794</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>515091</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7128269</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -3037,10 +3037,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120474982</v>
+        <v>120474995</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515116</v>
+        <v>515125</v>
       </c>
       <c r="R21" t="n">
-        <v>7128353</v>
+        <v>7128350</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120475900</v>
+        <v>120475794</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515034</v>
+        <v>515091</v>
       </c>
       <c r="R22" t="n">
-        <v>7128245</v>
+        <v>7128269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3215,6 +3215,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3241,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120475510</v>
+        <v>120474789</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3257,21 +3262,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3281,10 +3286,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515134</v>
+        <v>515098</v>
       </c>
       <c r="R23" t="n">
-        <v>7128286</v>
+        <v>7128433</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3317,6 +3322,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3343,7 +3353,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120474789</v>
+        <v>120474748</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3377,19 +3387,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515098</v>
+        <v>515115</v>
       </c>
       <c r="R24" t="n">
-        <v>7128433</v>
+        <v>7128454</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3423,7 +3438,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3450,10 +3465,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120475672</v>
+        <v>120474982</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3466,21 +3481,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3490,13 +3505,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515151</v>
+        <v>515116</v>
       </c>
       <c r="R25" t="n">
-        <v>7128276</v>
+        <v>7128353</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3526,11 +3541,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3557,10 +3567,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120474748</v>
+        <v>120475900</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3573,39 +3583,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515115</v>
+        <v>515034</v>
       </c>
       <c r="R26" t="n">
-        <v>7128454</v>
+        <v>7128245</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3638,11 +3643,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,10 +3669,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120474995</v>
+        <v>120475672</v>
       </c>
       <c r="B27" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515125</v>
+        <v>515151</v>
       </c>
       <c r="R27" t="n">
-        <v>7128350</v>
+        <v>7128276</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3745,6 +3745,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,10 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120474577</v>
+        <v>120474889</v>
       </c>
       <c r="B28" t="n">
-        <v>79527</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3783,25 +3788,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515097</v>
+        <v>515128</v>
       </c>
       <c r="R28" t="n">
-        <v>7128458</v>
+        <v>7128396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3847,6 +3852,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3873,10 +3883,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120474889</v>
+        <v>120475071</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>91146</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3885,25 +3895,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3913,10 +3923,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515128</v>
+        <v>515108</v>
       </c>
       <c r="R29" t="n">
-        <v>7128396</v>
+        <v>7128363</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3949,11 +3959,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,10 +3985,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120475071</v>
+        <v>120475510</v>
       </c>
       <c r="B30" t="n">
-        <v>91146</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3992,25 +3997,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4020,13 +4025,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515108</v>
+        <v>515134</v>
       </c>
       <c r="R30" t="n">
-        <v>7128363</v>
+        <v>7128286</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4194,10 +4199,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120475794</v>
+        <v>120474577</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>79527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4206,25 +4211,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4234,10 +4239,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515091</v>
+        <v>515097</v>
       </c>
       <c r="R32" t="n">
-        <v>7128269</v>
+        <v>7128458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4270,11 +4275,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -3246,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120474789</v>
+        <v>120474982</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3286,13 +3286,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515098</v>
+        <v>515116</v>
       </c>
       <c r="R23" t="n">
-        <v>7128433</v>
+        <v>7128353</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3322,11 +3322,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3353,7 +3348,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120474748</v>
+        <v>120474789</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3387,24 +3382,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515115</v>
+        <v>515098</v>
       </c>
       <c r="R24" t="n">
-        <v>7128454</v>
+        <v>7128433</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3438,7 +3428,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3465,10 +3455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120474982</v>
+        <v>120474748</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3481,34 +3471,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515116</v>
+        <v>515115</v>
       </c>
       <c r="R25" t="n">
-        <v>7128353</v>
+        <v>7128454</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,6 +3536,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -2925,10 +2925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120476080</v>
+        <v>120475071</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>91146</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2937,43 +2937,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515086</v>
+        <v>515108</v>
       </c>
       <c r="R20" t="n">
-        <v>7128233</v>
+        <v>7128363</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3006,11 +3001,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3139,10 +3129,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120475794</v>
+        <v>120475510</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3155,21 +3145,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3179,13 +3169,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515091</v>
+        <v>515134</v>
       </c>
       <c r="R22" t="n">
-        <v>7128269</v>
+        <v>7128286</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3215,11 +3205,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,10 +3231,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120474982</v>
+        <v>120475794</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3262,21 +3247,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3286,10 +3271,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515116</v>
+        <v>515091</v>
       </c>
       <c r="R23" t="n">
-        <v>7128353</v>
+        <v>7128269</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3322,6 +3307,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3455,10 +3445,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120474748</v>
+        <v>120474577</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3467,43 +3457,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515115</v>
+        <v>515097</v>
       </c>
       <c r="R25" t="n">
-        <v>7128454</v>
+        <v>7128458</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,11 +3521,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3567,10 +3547,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120475900</v>
+        <v>120476080</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3583,34 +3563,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515034</v>
+        <v>515086</v>
       </c>
       <c r="R26" t="n">
-        <v>7128245</v>
+        <v>7128233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3643,6 +3628,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3669,7 +3659,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120475672</v>
+        <v>120474395</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3703,16 +3693,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515151</v>
+        <v>515054</v>
       </c>
       <c r="R27" t="n">
-        <v>7128276</v>
+        <v>7128523</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3749,7 +3744,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3776,10 +3771,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120474889</v>
+        <v>120474982</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3792,21 +3787,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3816,10 +3811,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515128</v>
+        <v>515116</v>
       </c>
       <c r="R28" t="n">
-        <v>7128396</v>
+        <v>7128353</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3852,11 +3847,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3883,10 +3873,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120475071</v>
+        <v>120474748</v>
       </c>
       <c r="B29" t="n">
-        <v>91146</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3895,38 +3885,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515115</v>
       </c>
       <c r="R29" t="n">
-        <v>7128363</v>
+        <v>7128454</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3959,6 +3954,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,10 +3985,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120475510</v>
+        <v>120475672</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515134</v>
+        <v>515151</v>
       </c>
       <c r="R30" t="n">
-        <v>7128286</v>
+        <v>7128276</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4061,6 +4061,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,10 +4092,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120474395</v>
+        <v>120475900</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4103,42 +4108,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515054</v>
+        <v>515034</v>
       </c>
       <c r="R31" t="n">
-        <v>7128523</v>
+        <v>7128245</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4168,11 +4168,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4199,10 +4194,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120474577</v>
+        <v>120474889</v>
       </c>
       <c r="B32" t="n">
-        <v>79527</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4211,25 +4206,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4239,10 +4234,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515097</v>
+        <v>515128</v>
       </c>
       <c r="R32" t="n">
-        <v>7128458</v>
+        <v>7128396</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4275,6 +4270,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -2925,10 +2925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120475071</v>
+        <v>120475510</v>
       </c>
       <c r="B20" t="n">
-        <v>91146</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515108</v>
+        <v>515134</v>
       </c>
       <c r="R20" t="n">
-        <v>7128363</v>
+        <v>7128286</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120474995</v>
+        <v>120475794</v>
       </c>
       <c r="B21" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515125</v>
+        <v>515091</v>
       </c>
       <c r="R21" t="n">
-        <v>7128350</v>
+        <v>7128269</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3103,6 +3103,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3129,10 +3134,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120475510</v>
+        <v>120474789</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3145,21 +3150,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515134</v>
+        <v>515098</v>
       </c>
       <c r="R22" t="n">
-        <v>7128286</v>
+        <v>7128433</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3205,6 +3210,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3231,7 +3241,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120475794</v>
+        <v>120474395</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -3265,19 +3275,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515091</v>
+        <v>515054</v>
       </c>
       <c r="R23" t="n">
-        <v>7128269</v>
+        <v>7128523</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3311,7 +3326,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3338,10 +3353,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120474789</v>
+        <v>120474995</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3354,21 +3369,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3378,10 +3393,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515098</v>
+        <v>515125</v>
       </c>
       <c r="R24" t="n">
-        <v>7128433</v>
+        <v>7128350</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3414,11 +3429,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3547,7 +3557,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120476080</v>
+        <v>120474889</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3581,21 +3591,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515086</v>
+        <v>515128</v>
       </c>
       <c r="R26" t="n">
-        <v>7128233</v>
+        <v>7128396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3659,7 +3664,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120474395</v>
+        <v>120476080</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3704,13 +3709,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515054</v>
+        <v>515086</v>
       </c>
       <c r="R27" t="n">
-        <v>7128523</v>
+        <v>7128233</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3771,10 +3776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120474982</v>
+        <v>120475071</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>91146</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3783,25 +3788,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515116</v>
+        <v>515108</v>
       </c>
       <c r="R28" t="n">
-        <v>7128353</v>
+        <v>7128363</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3873,10 +3878,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120474748</v>
+        <v>120474982</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,39 +3894,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515115</v>
+        <v>515116</v>
       </c>
       <c r="R29" t="n">
-        <v>7128454</v>
+        <v>7128353</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3954,11 +3954,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3985,7 +3980,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120475672</v>
+        <v>120474748</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -4019,19 +4014,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515151</v>
+        <v>515115</v>
       </c>
       <c r="R30" t="n">
-        <v>7128276</v>
+        <v>7128454</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4194,7 +4194,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120474889</v>
+        <v>120475672</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -4234,13 +4234,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515128</v>
+        <v>515151</v>
       </c>
       <c r="R32" t="n">
-        <v>7128396</v>
+        <v>7128276</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -4202,7 +4202,7 @@
         <v>120475071</v>
       </c>
       <c r="B32" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 32152-2020 artfynd.xlsx
+++ b/artfynd/A 32152-2020 artfynd.xlsx
@@ -4202,7 +4202,7 @@
         <v>120475071</v>
       </c>
       <c r="B32" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
